--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104544_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104544_W10.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6805</v>
+        <v>4.7474</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6885</v>
+        <v>1.7778</v>
       </c>
       <c r="F2" t="n">
-        <v>1.992</v>
+        <v>2.9696</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5781</v>
+        <v>2.7228</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9378</v>
+        <v>3.2634</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3598</v>
+        <v>-0.5406</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0975</v>
+        <v>1.9011</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9482</v>
+        <v>2.0577</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1493</v>
+        <v>-0.1566</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4806</v>
+        <v>0.8217</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9896</v>
+        <v>1.2057</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.509</v>
+        <v>-0.384</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4446</v>
+        <v>0.1824</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0162</v>
+        <v>-0.0746</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4284</v>
+        <v>0.257</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.2495</v>
+        <v>0.9317</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.06419999999999999</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1853</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7076</v>
+        <v>4.3838</v>
       </c>
       <c r="E3" t="n">
-        <v>2.048</v>
+        <v>3.0711</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6597</v>
+        <v>1.3127</v>
       </c>
       <c r="G3" t="n">
-        <v>2.732</v>
+        <v>4.5864</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2757</v>
+        <v>4.9344</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5437</v>
+        <v>-0.3481</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9291</v>
+        <v>4.079</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0811</v>
+        <v>3.93</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.152</v>
+        <v>0.1489</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8028</v>
+        <v>0.5074</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1946</v>
+        <v>1.0044</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3918</v>
+        <v>-0.497</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1364</v>
+        <v>1.1373</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1603</v>
+        <v>0.4294</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0239</v>
+        <v>0.7079</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9320000000000001</v>
+        <v>-2.2504</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7143</v>
+        <v>3.4611</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5645</v>
+        <v>1.4098</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1498</v>
+        <v>2.0512</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6103</v>
+        <v>1.6009</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8787</v>
+        <v>3.8774</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2684</v>
+        <v>-2.2765</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2865</v>
+        <v>2.2583</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3768</v>
+        <v>3.3612</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6762</v>
+        <v>-0.6574</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6484</v>
+        <v>0.4065</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0907</v>
+        <v>-0.0258</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5577</v>
+        <v>0.4324</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6735</v>
+        <v>3.3673</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5043</v>
+        <v>2.8442</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1692</v>
+        <v>0.5232</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4698</v>
+        <v>3.4905</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4413</v>
+        <v>1.4554</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0285</v>
+        <v>2.0351</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2978</v>
+        <v>3.287</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5066</v>
+        <v>1.4996</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M5" t="n">
-        <v>0.172</v>
+        <v>0.2035</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0653</v>
+        <v>-0.0442</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2914</v>
+        <v>-0.6271</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8861</v>
+        <v>-0.5323</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4053</v>
+        <v>-0.0948</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6041</v>
+        <v>2.7489</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2742</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3299</v>
+        <v>2.1365</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8787</v>
+        <v>1.8905</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0031</v>
+        <v>0.0107</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8818</v>
+        <v>1.8798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8968</v>
+        <v>0.8845</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7409</v>
+        <v>0.7294</v>
       </c>
       <c r="M6" t="n">
-        <v>0.982</v>
+        <v>1.006</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1159</v>
+        <v>0.0177</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3297</v>
+        <v>0.0253</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2138</v>
+        <v>-0.0077</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SYLLA</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5037</v>
+        <v>1.8598</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0903</v>
+        <v>-1.7239</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4134</v>
+        <v>3.5836</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9276</v>
+        <v>1.2251</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4184</v>
+        <v>1.2122</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5091</v>
+        <v>0.0129</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9134</v>
+        <v>1.2216</v>
       </c>
       <c r="K7" t="n">
-        <v>0.876</v>
+        <v>0.7682</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.4534</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0142</v>
+        <v>0.0035</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4576</v>
+        <v>0.444</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4718</v>
+        <v>-0.4405</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-5.0079</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>3.1868</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9618</v>
+        <v>0.4345</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0162</v>
+        <v>-0.1165</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0544</v>
+        <v>0.551</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>2.0212</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>A. SYLLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0707</v>
+        <v>1.5618</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6561</v>
+        <v>1.1342</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7267</v>
+        <v>0.4277</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2389</v>
+        <v>0.9303</v>
       </c>
       <c r="H8" t="n">
-        <v>1.215</v>
+        <v>0.4193</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0239</v>
+        <v>0.511</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2669</v>
+        <v>0.9023</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7926</v>
+        <v>0.8651</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4743</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.028</v>
+        <v>0.028</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4224</v>
+        <v>-0.4458</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4504</v>
+        <v>0.4738</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.9903</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1757</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6218</v>
+        <v>0.0185</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1179</v>
+        <v>0.0741</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7398</v>
+        <v>-0.0556</v>
       </c>
       <c r="V8" t="n">
-        <v>2.0246</v>
+        <v>0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6548</v>
+        <v>0.5656</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1218</v>
+        <v>-0.1222</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7766</v>
+        <v>0.6878</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1428</v>
+        <v>0.1463</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1717</v>
+        <v>-0.1696</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2852</v>
+        <v>0.1917</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0877</v>
+        <v>0.0882</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1975</v>
+        <v>0.1035</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2083</v>
+        <v>0.5216</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.058</v>
+        <v>-1.6113</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8497</v>
+        <v>2.1329</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1843</v>
+        <v>2.1916</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4646</v>
+        <v>1.4675</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7197</v>
+        <v>0.7241</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0582</v>
+        <v>2.045</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7895</v>
+        <v>0.7789</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M10" t="n">
-        <v>0.126</v>
+        <v>0.1467</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6751</v>
+        <v>0.6886</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8462</v>
+        <v>-0.1253</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4869</v>
+        <v>-0.0141</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3593</v>
+        <v>-0.1111</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.167</v>
+        <v>-1.6046</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6031</v>
+        <v>-3.2906</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4361</v>
+        <v>1.6859</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4338</v>
+        <v>-1.4364</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0716</v>
+        <v>-1.0772</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6804</v>
+        <v>-1.7109</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6274</v>
+        <v>-0.6452</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.053</v>
+        <v>-1.0656</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2466</v>
+        <v>0.2745</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2652</v>
+        <v>0.2861</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1454</v>
+        <v>-0.5748</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.747</v>
+        <v>-0.3929</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3983</v>
+        <v>-0.1819</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2567</v>
+        <v>-3.6339</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5905</v>
+        <v>-3.2838</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6663</v>
+        <v>-0.3502</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3382</v>
+        <v>-0.3322</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4631</v>
+        <v>-1.4647</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1249</v>
+        <v>1.1324</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7421</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4138</v>
+        <v>-1.4349</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4038</v>
+        <v>0.4324</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0494</v>
+        <v>-0.0298</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9282</v>
+        <v>-0.2938</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8166</v>
+        <v>-0.4626</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1116</v>
+        <v>0.1688</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.9772</v>
+        <v>17.9788</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1403</v>
+        <v>0.8176999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>16.8368</v>
+        <v>17.1609</v>
       </c>
       <c r="G13" t="n">
-        <v>16.9905</v>
+        <v>17.0158</v>
       </c>
       <c r="H13" t="n">
-        <v>14.6314</v>
+        <v>14.6468</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3589</v>
+        <v>2.3688</v>
       </c>
       <c r="J13" t="n">
-        <v>14.341</v>
+        <v>14.1205</v>
       </c>
       <c r="K13" t="n">
-        <v>11.5028</v>
+        <v>11.3529</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8382</v>
+        <v>2.7676</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6493</v>
+        <v>2.8953</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1284</v>
+        <v>3.294</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4792</v>
+        <v>-0.3986</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1343</v>
+        <v>-1.138300000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.415</v>
+        <v>-20.487</v>
       </c>
       <c r="R13" t="n">
-        <v>19.2809</v>
+        <v>19.3487</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7710999999999996</v>
+        <v>0.7675999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0131</v>
+        <v>-1.0018</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7844</v>
+        <v>1.7695</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3499</v>
+        <v>1.3336</v>
       </c>
       <c r="W13" t="n">
-        <v>8.2273</v>
+        <v>8.186</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.8774</v>
+        <v>-6.8524</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4231</v>
+        <v>4.549</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3738</v>
+        <v>2.4787</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0493</v>
+        <v>2.0704</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0228</v>
+        <v>2.0246</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5137</v>
+        <v>1.5136</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5091</v>
+        <v>0.511</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9768</v>
+        <v>1.9678</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9395</v>
+        <v>1.9305</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M14" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6639</v>
+        <v>-0.547</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4688</v>
+        <v>-0.351</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1951</v>
+        <v>-0.1961</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7032</v>
+        <v>1.7057</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8029</v>
+        <v>2.1429</v>
       </c>
       <c r="E15" t="n">
-        <v>1.231</v>
+        <v>1.4515</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5719</v>
+        <v>0.6914</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8643</v>
+        <v>0.8726</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8096</v>
+        <v>-0.8017</v>
       </c>
       <c r="I15" t="n">
-        <v>1.674</v>
+        <v>1.6743</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9746</v>
+        <v>1.963</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1834</v>
+        <v>0.1756</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1103</v>
+        <v>-1.0904</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8099</v>
+        <v>-0.4809</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6775</v>
+        <v>-0.4416</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1325</v>
+        <v>-0.0392</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2147</v>
+        <v>-0.4716</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8619</v>
+        <v>0.0322</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6472</v>
+        <v>-0.5039</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8105</v>
+        <v>-1.8023</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6479</v>
+        <v>-1.6431</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1626</v>
+        <v>-0.1592</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.103</v>
+        <v>-0.1091</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L16" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7075</v>
+        <v>-1.6932</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.891</v>
+        <v>0.1925</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9648</v>
+        <v>0.1414</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4514</v>
+        <v>-0.6564</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.833</v>
+        <v>-0.9731</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3816</v>
+        <v>0.3167</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7735</v>
+        <v>0.778</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7432</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5167</v>
+        <v>1.5164</v>
       </c>
       <c r="J17" t="n">
-        <v>1.396</v>
+        <v>1.3802</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3912</v>
+        <v>0.3825</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0048</v>
+        <v>0.9977</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.6022</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5483</v>
+        <v>0.3379</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0393</v>
+        <v>-0.077</v>
       </c>
       <c r="U17" t="n">
-        <v>0.509</v>
+        <v>0.4149</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5083</v>
+        <v>-1.5347</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.042</v>
+        <v>1.1398</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5337</v>
+        <v>-2.6745</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5228</v>
+        <v>-1.5999</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.062</v>
+        <v>-1.433</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4608</v>
+        <v>-0.1669</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2284</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1008</v>
+        <v>-0.1109</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1276</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2944</v>
+        <v>-2.2929</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-1.3221</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3331</v>
+        <v>-0.9708</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>0.973</v>
+        <v>0.015</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5474</v>
+        <v>-0.0492</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4255</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7531</v>
+        <v>-2.2762</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0605</v>
+        <v>-2.7785</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8136</v>
+        <v>0.5023</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5952</v>
+        <v>-2.5302</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4299</v>
+        <v>-1.0626</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1653</v>
+        <v>-1.4676</v>
       </c>
       <c r="J19" t="n">
-        <v>0.725</v>
+        <v>-1.2543</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0906</v>
+        <v>-0.1142</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8156</v>
+        <v>-1.1401</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3202</v>
+        <v>-1.2759</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3393</v>
+        <v>-0.9485</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9808</v>
+        <v>-0.3275</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.5039</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1975</v>
+        <v>0.2053</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1693</v>
+        <v>-0.1584</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0281</v>
+        <v>0.3637</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5068</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>K. ZORIKS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5181</v>
+        <v>-2.4048</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9082</v>
+        <v>-1.7145</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3901</v>
+        <v>-0.6903</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.205</v>
+        <v>-2.449</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.759</v>
+        <v>0.784</v>
       </c>
       <c r="I20" t="n">
-        <v>1.554</v>
+        <v>-3.233</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4093</v>
+        <v>-0.3994</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4515</v>
+        <v>1.7614</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0422</v>
+        <v>-2.1608</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7957</v>
+        <v>-2.0496</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3075</v>
+        <v>-0.9774</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5118</v>
+        <v>-1.0722</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6293</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5943000000000001</v>
+        <v>-0.3428</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0302</v>
+        <v>-0.1282</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6245000000000001</v>
+        <v>-0.2146</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6874</v>
+        <v>-3.4606</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.982</v>
+        <v>-2.0031</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7053</v>
+        <v>-1.4575</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7721</v>
+        <v>-1.7729</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.1715</v>
+        <v>-3.1763</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3994</v>
+        <v>1.4034</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9386</v>
+        <v>-0.9575</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.7298</v>
+        <v>-2.7449</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8335</v>
+        <v>-0.8154</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2701</v>
+        <v>0.4912</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0907</v>
+        <v>0.0926</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1793</v>
+        <v>0.3986</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. ZORIKS</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7207</v>
+        <v>-4.024</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4954</v>
+        <v>-4.2916</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2253</v>
+        <v>0.2676</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4365</v>
+        <v>-1.1982</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7835</v>
+        <v>-2.7518</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.2201</v>
+        <v>1.5537</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3641</v>
+        <v>-0.4237</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7765</v>
+        <v>-1.4586</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1406</v>
+        <v>1.035</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0725</v>
+        <v>-0.7745</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.993</v>
+        <v>-1.2932</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0795</v>
+        <v>0.5187</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6698</v>
+        <v>0.0847</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9557</v>
+        <v>-0.3836</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7141</v>
+        <v>0.4683</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.811</v>
+        <v>-4.142</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6635</v>
+        <v>-5.1163</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8524</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.5606</v>
+        <v>-5.5785</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4499</v>
+        <v>-2.4635</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.1107</v>
+        <v>-3.115</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.8931</v>
+        <v>-3.9302</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.646</v>
+        <v>-1.6729</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6675</v>
+        <v>-1.6483</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.2464</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9557</v>
+        <v>-0.3651</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0248</v>
+        <v>0.1187</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9681</v>
+        <v>-4.9108</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4401</v>
+        <v>-5.3861</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4721</v>
+        <v>0.4753</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.7482</v>
+        <v>-3.7599</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.8553</v>
+        <v>-2.8739</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8929</v>
+        <v>-0.886</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7853</v>
+        <v>-1.825</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1855</v>
+        <v>-1.2215</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9629</v>
+        <v>-1.935</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6698</v>
+        <v>-1.6524</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2241</v>
+        <v>0.3123</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1693</v>
+        <v>-0.0492</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3935</v>
+        <v>0.3616</v>
       </c>
       <c r="V24" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.9774</v>
+        <v>-17.1892</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.837</v>
+        <v>-17.161</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1403</v>
+        <v>-0.02819999999999995</v>
       </c>
       <c r="G25" t="n">
-        <v>-16.9903</v>
+        <v>-17.0157</v>
       </c>
       <c r="H25" t="n">
-        <v>-14.6311</v>
+        <v>-14.6467</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.3592</v>
+        <v>-2.368900000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.649400000000001</v>
+        <v>-2.8952</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.1285</v>
+        <v>-3.293799999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4792000000000002</v>
+        <v>0.3987000000000002</v>
       </c>
       <c r="M25" t="n">
-        <v>-14.341</v>
+        <v>-14.1206</v>
       </c>
       <c r="N25" t="n">
-        <v>-11.5026</v>
+        <v>-11.3531</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.8382</v>
+        <v>-2.7677</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-19.2807</v>
+        <v>-19.3487</v>
       </c>
       <c r="R25" t="n">
-        <v>20.4151</v>
+        <v>20.4869</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7712</v>
+        <v>0.02179999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.7843</v>
+        <v>-1.7693</v>
       </c>
       <c r="U25" t="n">
-        <v>1.013</v>
+        <v>1.7913</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.3501</v>
+        <v>-1.3336</v>
       </c>
       <c r="W25" t="n">
-        <v>6.8774</v>
+        <v>6.852399999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.227499999999999</v>
+        <v>-8.1859</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104544_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104544_W10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.8524</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104544_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.1859</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
